--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45076</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45058</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44881</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44813</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45692</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45548</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44901</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44064</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44151</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44172</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44083</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44270</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>44217</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44061</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44194</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44203</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44210</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44180</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>44203</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44517</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44187</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44127</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44336</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44720</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44601</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44146</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44532</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44585</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44084</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44729</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44572</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44188</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44224</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44151</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44153</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44460</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44208</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44152</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44186</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44763</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44169</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44381</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44069.50508101852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44347</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44209</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44854</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44200</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44859</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44147</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44153</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44153</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44127</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44389</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44153</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44326</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44125</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44603</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44103</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44839</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44083</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44119</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44452</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44105</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44279</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44295</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44799</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44299</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44365</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44438</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44488</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44796</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44722</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44370</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44195</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44522</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44452</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44728</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44785.455</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44208</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44536</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44166</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44076</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44127</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44133</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44480</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44452</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44509</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44165</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44480</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44467</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44712</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44729</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44147</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44242</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44180</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44119</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44279</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44062</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44088</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44879</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44218</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44636</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44496</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44371</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45085</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44055</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45258</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45617</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45342</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45342</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45758.52722222222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45335</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44488</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45251</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45243</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45180</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45016</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45405</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44454</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44267</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45202</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45366</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45219</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45733</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44595</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45107</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45183</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45187.4346412037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45243</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44895</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45761</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45104</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45299</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45264</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45646</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45107</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45579</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45680</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44818</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45436</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44720</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45461</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45110</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45212</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45366</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45450</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45540</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45239</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>44880</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45107</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45240</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45091</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45194</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45352</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45548</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45258</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45754</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44526</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>44945</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45163</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>44133</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45779.64287037037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45428</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>44151</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44407</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44595</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45453</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45149</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45187</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45366</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45786.59866898148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45428</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>44076</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45155</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45461</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45643</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45534</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44594</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45043</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44532</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44914</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45161</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45758.52923611111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45366</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45643</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>44151</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45527.45688657407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45793</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44137</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45796</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>44967</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44203</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45366</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45701</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44162</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44620</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>44161</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44187</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45485</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44671</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44279</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45212</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44894</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45448</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44239</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45257</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44897</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45607</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45180</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44706</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44167</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45799</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45415</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44505</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45547</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45840</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45123</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45211</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45800</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45793</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45351</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45845</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44952</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45240</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44203</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45433</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45205</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45208</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44631</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44489</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45848</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44511</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45238</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45246</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45702</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44791</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45631</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45204</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45169</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45205</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45762</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43223,7 +43223,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45331</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45853</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45246</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43808,7 +43808,7 @@
         <v>45779</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45719</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>44796</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45740</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45149</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>44110</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44806</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45758.495625</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45251</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>44383</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>44840</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44370</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45545</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45453</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44830</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>44381</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>44382</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45827</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47702,7 +47702,7 @@
         <v>45646</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>45827</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47816,7 +47816,7 @@
         <v>45827</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45827</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45660</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>44364</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>44944</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45114</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>44883</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45061</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>44732</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45244</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>44070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45737</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45548</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>44908</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>44862</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44515</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44879</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44204</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45008</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>44239</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>44805</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>44916</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>44160</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>45097</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>44662</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51814,7 +51814,7 @@
         <v>44886</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45219</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45016</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45229</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45223</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>44967</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45097</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45189</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45016</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>45016</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>44267</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>45219</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45310</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45215</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53663,7 +53663,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
         <v>45076</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         <v>45058</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44881</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44813</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45692</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>45548</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>44901</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44064</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44151</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44172</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44083</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44270</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3345,7 +3345,7 @@
         <v>44217</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44061</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44194</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44203</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44210</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44180</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>44203</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44517</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44187</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44127</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44336</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44720</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44601</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44146</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44532</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44585</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44084</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44729</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44572</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44188</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44224</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44151</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44153</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44460</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44208</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44152</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44186</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44763</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44169</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44381</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44069.50508101852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44347</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44209</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44854</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44200</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44859</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44147</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44153</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44153</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44127</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44389</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44153</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44326</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44125</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44603</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>44103</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>44839</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44083</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>44148</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         <v>44650</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>44119</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44452</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>44105</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>44279</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>44295</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>44799</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44299</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>44365</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         <v>44438</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>44488</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>44796</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10471,7 +10471,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10528,7 +10528,7 @@
         <v>44722</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>44370</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>44195</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44522</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44452</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44728</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44785.455</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44208</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44536</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44166</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11455,7 +11455,7 @@
         <v>44076</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44127</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>44133</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>44480</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>44452</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>44509</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11797,7 +11797,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>44165</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>44480</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>44467</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44712</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12149,7 +12149,7 @@
         <v>44729</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12268,7 +12268,7 @@
         <v>44147</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         <v>44242</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>44180</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12439,7 +12439,7 @@
         <v>44119</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44279</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44062</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44088</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44879</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44218</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44636</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44496</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44371</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>45085</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44055</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45258</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45617</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -13998,7 +13998,7 @@
         <v>45342</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45342</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45758.52722222222</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45335</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>44488</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45251</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45747</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45243</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45180</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15857,7 +15857,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45016</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16204,7 +16204,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16318,7 +16318,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45405</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>44454</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44267</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45202</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45366</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45219</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45733</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44595</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45107</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45183</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45187.4346412037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45243</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>44895</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45761</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45104</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45299</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18395,7 +18395,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45264</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18799,7 +18799,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18856,7 +18856,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45646</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45107</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19431,7 +19431,7 @@
         <v>45579</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19493,7 +19493,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>45680</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19607,7 +19607,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>44818</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45436</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44720</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>45461</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45110</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45212</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45366</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45450</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45540</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45239</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         <v>45223</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21248,7 +21248,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21310,7 +21310,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>44880</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21600,7 +21600,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21776,7 +21776,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         <v>45107</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22004,7 +22004,7 @@
         <v>45240</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45091</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>45194</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22408,7 +22408,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22465,7 +22465,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22636,7 +22636,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22983,7 +22983,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>44130</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45352</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45548</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23449,7 +23449,7 @@
         <v>45258</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45754</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23677,7 +23677,7 @@
         <v>44526</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>44945</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45163</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>44133</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>45779.64287037037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45428</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>44151</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25288,7 +25288,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>44407</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25402,7 +25402,7 @@
         <v>44595</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26096,7 +26096,7 @@
         <v>45453</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26153,7 +26153,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>45149</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45187</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45366</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45786.59866898148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45428</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>44076</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45155</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27360,7 +27360,7 @@
         <v>45461</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27474,7 +27474,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>45643</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45534</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44594</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45043</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>44532</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>44914</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45161</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45758.52923611111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45366</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44596</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45643</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30188,7 +30188,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30245,7 +30245,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>44151</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30473,7 +30473,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30649,7 +30649,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30706,7 +30706,7 @@
         <v>45527.45688657407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30944,7 +30944,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>45793</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>44137</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31172,7 +31172,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31229,7 +31229,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>45796</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>44967</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31457,7 +31457,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31519,7 +31519,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31581,7 +31581,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31695,7 +31695,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31752,7 +31752,7 @@
         <v>44203</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45366</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32104,7 +32104,7 @@
         <v>45037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32337,7 +32337,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45701</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>44162</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44620</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>44161</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44187</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32912,7 +32912,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32969,7 +32969,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45485</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33140,7 +33140,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33197,7 +33197,7 @@
         <v>44671</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33254,7 +33254,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>44279</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33435,7 +33435,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33678,7 +33678,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33792,7 +33792,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34020,7 +34020,7 @@
         <v>45212</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>44894</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45448</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34590,7 +34590,7 @@
         <v>44239</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>45222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34761,7 +34761,7 @@
         <v>45257</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34818,7 +34818,7 @@
         <v>44897</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34875,7 +34875,7 @@
         <v>45607</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34932,7 +34932,7 @@
         <v>45180</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34989,7 +34989,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35046,7 +35046,7 @@
         <v>44706</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35103,7 +35103,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35222,7 +35222,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44167</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35745,7 +35745,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35926,7 +35926,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>45799</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36040,7 +36040,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45415</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44505</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45547</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>45840</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45123</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>45211</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45800</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45793</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45351</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45845</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38360,7 +38360,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>44952</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45240</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44203</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45433</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45205</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45208</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39458,7 +39458,7 @@
         <v>44631</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>44489</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45848</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44511</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45238</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45246</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45702</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>44791</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41478,7 +41478,7 @@
         <v>44839</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>45631</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>45852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41939,7 +41939,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41996,7 +41996,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45810</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42291,7 +42291,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42348,7 +42348,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42405,7 +42405,7 @@
         <v>45204</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45169</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45205</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42633,7 +42633,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42690,7 +42690,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42747,7 +42747,7 @@
         <v>45762</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42985,7 +42985,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43223,7 +43223,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45331</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>45853</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43456,7 +43456,7 @@
         <v>45246</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43513,7 +43513,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43808,7 +43808,7 @@
         <v>45779</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45719</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44150,7 +44150,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44269,7 +44269,7 @@
         <v>44796</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45740</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>45149</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44854,7 +44854,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>44110</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44806</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45758.495625</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45251</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45434,7 +45434,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45491,7 +45491,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>44383</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>44840</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>44370</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45957,7 +45957,7 @@
         <v>45545</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46019,7 +46019,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46133,7 +46133,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46247,7 +46247,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46309,7 +46309,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46366,7 +46366,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46428,7 +46428,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46485,7 +46485,7 @@
         <v>45453</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46547,7 +46547,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46609,7 +46609,7 @@
         <v>44830</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46666,7 +46666,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46723,7 +46723,7 @@
         <v>44381</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46780,7 +46780,7 @@
         <v>44382</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46842,7 +46842,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46899,7 +46899,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46956,7 +46956,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47013,7 +47013,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47070,7 +47070,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47127,7 +47127,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47184,7 +47184,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47246,7 +47246,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47303,7 +47303,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47360,7 +47360,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47417,7 +47417,7 @@
         <v>45827</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47531,7 +47531,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47588,7 +47588,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47645,7 +47645,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47702,7 +47702,7 @@
         <v>45646</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>45827</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47816,7 +47816,7 @@
         <v>45827</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47873,7 +47873,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45827</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45660</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>44364</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>44944</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>45114</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48562,7 +48562,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>44883</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45061</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48909,7 +48909,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49033,7 +49033,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>44732</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45244</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49675,7 +49675,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49732,7 +49732,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49789,7 +49789,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49846,7 +49846,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49908,7 +49908,7 @@
         <v>44070</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49965,7 +49965,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50079,7 +50079,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50136,7 +50136,7 @@
         <v>45737</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50193,7 +50193,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50307,7 +50307,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50364,7 +50364,7 @@
         <v>45548</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50426,7 +50426,7 @@
         <v>44908</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50483,7 +50483,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50597,7 +50597,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>44862</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50711,7 +50711,7 @@
         <v>44515</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50773,7 +50773,7 @@
         <v>44879</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50835,7 +50835,7 @@
         <v>44204</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45008</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51011,7 +51011,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>44239</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>44805</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51182,7 +51182,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>44916</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51296,7 +51296,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>44160</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51410,7 +51410,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51472,7 +51472,7 @@
         <v>45097</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51529,7 +51529,7 @@
         <v>45205</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51586,7 +51586,7 @@
         <v>44662</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51757,7 +51757,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51814,7 +51814,7 @@
         <v>44886</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45219</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45016</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45229</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45223</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52332,7 +52332,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52389,7 +52389,7 @@
         <v>44967</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52446,7 +52446,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52560,7 +52560,7 @@
         <v>45097</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52617,7 +52617,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52798,7 +52798,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45189</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52912,7 +52912,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>45016</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>45016</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53088,7 +53088,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53145,7 +53145,7 @@
         <v>44267</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53202,7 +53202,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53373,7 +53373,7 @@
         <v>45219</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53430,7 +53430,7 @@
         <v>45310</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45215</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53549,7 +53549,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53663,7 +53663,7 @@
         <v>45176</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44382</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>44432</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>45058</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45076</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44813</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>45548</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44901</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45692</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44064</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44151</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44172</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44083</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44270</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44217</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44176</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44061</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44194</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44203</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44210</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44180</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>44203</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44517</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44127</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44336</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44187</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44720</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44601</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44146</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44532</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44585</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44084</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44729</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44572</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44188</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44224</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44151</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44153</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44460</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44208</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44152</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44186</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44763</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44169</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44381</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44069.50508101852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44347</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44854</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44200</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44209</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44859</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44147</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44153</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44153</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44127</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44389</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44153</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44125</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44452</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44279</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44799</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44299</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44365</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44295</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44438</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44370</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44488</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44796</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44722</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44195</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44522</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44728</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44785.455</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44452</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44208</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44536</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44166</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44076</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44127</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44133</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44480</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44452</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>44509</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44165</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44729</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44480</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44467</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44147</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44242</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44180</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44119</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44279</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44062</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44218</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44879</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44636</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44496</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44326</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44103</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44839</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44083</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44650</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44119</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44603</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44105</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45405</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44267</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45107</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45366</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45240</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45219</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45335</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45548</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45251</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45747</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45258</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45754</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45243</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>44895</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44945</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45352</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45104</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45779.64287037037</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45163</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45428</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44151</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44595</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45453</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45149</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45187</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45786.59866898148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45428</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44076</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45461</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45534</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45643</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45043</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45161</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45758.52923611111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44914</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45366</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>44151</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45793</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44137</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45796</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44596</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44162</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44620</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45485</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45643</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44894</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45366</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45799</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45800</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44671</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45845</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45607</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45180</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45436</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45848</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44167</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45110</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45246</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45547</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45211</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45351</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45240</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>44203</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45433</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45205</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45208</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45852</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44130</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45238</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45762</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44526</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45779</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44133</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>44407</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44791</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45219</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45740</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45204</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45366</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45331</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45246</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45155</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45827</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45827</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>44594</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45719</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45827</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45827</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45149</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44806</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45758.495625</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45061</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45251</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44840</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45453</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45853</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44830</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45114</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45793</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45840</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>44732</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45527.45688657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45244</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45205</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>45882</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>44967</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>44203</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>44070</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45701</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45883.375</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44187</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45737</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45548</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45212</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>44908</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45448</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>44862</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>44515</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44879</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>44239</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44204</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45257</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44897</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45008</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44706</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>44239</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44805</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>44916</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45415</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>44160</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>44505</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45123</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45097</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44952</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45205</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>44662</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>44631</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>44489</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>44511</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>44886</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45219</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45016</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45229</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>45223</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>44967</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45097</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45702</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>44839</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45631</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45169</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45189</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45016</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45016</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>44267</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>44796</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45219</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44110</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45215</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45176</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>44383</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44370</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45545</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>44381</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>44382</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45085</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45258</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45617</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45646</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45342</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45342</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45660</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>44364</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>44944</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45180</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>44371</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45758.52722222222</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45202</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44488</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45733</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45107</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45243</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45183</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45016</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45187.4346412037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>44454</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44595</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45579</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45680</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>44818</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45761</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>44720</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>45461</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>45264</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45646</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45366</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45450</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45540</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45107</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45239</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>44880</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45091</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45194</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>45810</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         <v>44382</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>44432</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>45058</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45076</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>44813</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>45548</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44901</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45692</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44064</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44151</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44172</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44083</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44270</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>44217</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44176</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3407,7 +3407,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>44061</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>44194</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>44203</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>44210</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
         <v>44180</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>44203</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44517</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44127</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44336</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44187</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44720</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44601</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44146</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4795,7 +4795,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
         <v>44532</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44585</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>44084</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44729</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44572</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44188</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44224</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5774,7 +5774,7 @@
         <v>44151</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>44153</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44460</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6406,7 +6406,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6525,7 +6525,7 @@
         <v>44208</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>44152</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44186</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44763</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44169</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44875</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44381</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>44069.50508101852</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44347</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44854</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44200</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44209</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44859</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44517</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44517</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>44147</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44153</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44153</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44127</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44389</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44153</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>44147</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44125</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8902,7 +8902,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9016,7 +9016,7 @@
         <v>44148</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44452</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>44279</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44799</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44299</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44365</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44295</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44438</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44370</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44488</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44796</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44722</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44195</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44522</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44728</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44785.455</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>44452</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44208</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44536</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44166</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44076</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44127</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44133</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44480</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44452</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>44509</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44165</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11160,7 +11160,7 @@
         <v>44729</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44480</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44467</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44712</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44147</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44242</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44180</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11688,7 +11688,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11745,7 +11745,7 @@
         <v>44119</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44279</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44062</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12040,7 +12040,7 @@
         <v>44088</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44218</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44879</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44636</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44496</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44326</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44103</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44839</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44083</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44650</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44119</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44603</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44105</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45405</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44267</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45107</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14412,7 +14412,7 @@
         <v>45366</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         <v>45240</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>45219</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14583,7 +14583,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>45335</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>45548</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45251</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>45747</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15391,7 +15391,7 @@
         <v>45258</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15505,7 +15505,7 @@
         <v>45754</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45243</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15676,7 +15676,7 @@
         <v>44895</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15733,7 +15733,7 @@
         <v>44945</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>45352</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15847,7 +15847,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45104</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16194,7 +16194,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16427,7 +16427,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16712,7 +16712,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45779.64287037037</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45163</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45428</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44151</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>44595</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45453</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18499,7 +18499,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45149</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45187</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18955,7 +18955,7 @@
         <v>45786.59866898148</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>45428</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44076</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45461</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45534</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19711,7 +19711,7 @@
         <v>45643</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
         <v>45043</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45161</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45758.52923611111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44532</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20296,7 +20296,7 @@
         <v>44914</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45366</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20695,7 +20695,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>44151</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21208,7 +21208,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21493,7 +21493,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21607,7 +21607,7 @@
         <v>45793</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44137</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21778,7 +21778,7 @@
         <v>45796</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21835,7 +21835,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>44596</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22177,7 +22177,7 @@
         <v>44162</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>44620</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>45485</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>45643</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>44279</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22695,7 +22695,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22809,7 +22809,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>44894</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45366</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23213,7 +23213,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>45799</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23622,7 +23622,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>44161</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45800</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>44671</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45845</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24730,7 +24730,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24958,7 +24958,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>45222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>45607</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>45180</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25766,7 +25766,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45436</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45848</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26066,7 +26066,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44167</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26237,7 +26237,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26294,7 +26294,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45110</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26760,7 +26760,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>45246</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45547</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27112,7 +27112,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27169,7 +27169,7 @@
         <v>45211</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45351</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45240</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>44203</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45433</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45205</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>45208</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28614,7 +28614,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>45852</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28852,7 +28852,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44130</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>45810</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45238</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45762</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>44526</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45779</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30493,7 +30493,7 @@
         <v>44133</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30835,7 +30835,7 @@
         <v>44407</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44791</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31410,7 +31410,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45219</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45740</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>45204</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>45366</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32404,7 +32404,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32632,7 +32632,7 @@
         <v>45331</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32689,7 +32689,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32746,7 +32746,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32865,7 +32865,7 @@
         <v>45246</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32979,7 +32979,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45155</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45827</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45827</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>44594</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45719</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45827</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34409,7 +34409,7 @@
         <v>45827</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34585,7 +34585,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34756,7 +34756,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34813,7 +34813,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>45149</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>44806</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45758.495625</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45061</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45251</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35792,7 +35792,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35906,7 +35906,7 @@
         <v>44840</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45453</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45853</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44830</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45114</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>44883</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45793</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38147,7 +38147,7 @@
         <v>45840</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>44732</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45527.45688657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45244</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38841,7 +38841,7 @@
         <v>45205</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38898,7 +38898,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>45882</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39131,7 +39131,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39188,7 +39188,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39245,7 +39245,7 @@
         <v>44967</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39364,7 +39364,7 @@
         <v>44203</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39545,7 +39545,7 @@
         <v>45037</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>44070</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45701</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40011,7 +40011,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40068,7 +40068,7 @@
         <v>45883.375</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40125,7 +40125,7 @@
         <v>44187</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40239,7 +40239,7 @@
         <v>45737</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40296,7 +40296,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40472,7 +40472,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40529,7 +40529,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45548</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45212</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>44908</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45448</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>44862</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>44515</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41508,7 +41508,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>44879</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>44239</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44204</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45257</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44897</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>45008</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44706</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>44239</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>44805</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>44916</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42487,7 +42487,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42601,7 +42601,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42658,7 +42658,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>45415</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42772,7 +42772,7 @@
         <v>44160</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42829,7 +42829,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>44505</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43072,7 +43072,7 @@
         <v>45123</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43129,7 +43129,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45097</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44952</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43652,7 +43652,7 @@
         <v>45205</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43709,7 +43709,7 @@
         <v>44662</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43766,7 +43766,7 @@
         <v>44631</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43823,7 +43823,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>44489</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43994,7 +43994,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>44511</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>44886</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>45219</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44403,7 +44403,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44460,7 +44460,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44745,7 +44745,7 @@
         <v>45016</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44802,7 +44802,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45229</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>45223</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>44967</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45097</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45702</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>44839</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45631</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45169</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45189</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45016</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>45016</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46589,7 +46589,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>44267</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>44796</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45219</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45310</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>44110</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>45215</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45176</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>44383</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47635,7 +47635,7 @@
         <v>44370</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45545</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47930,7 +47930,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47987,7 +47987,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48044,7 +48044,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48101,7 +48101,7 @@
         <v>44381</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48158,7 +48158,7 @@
         <v>44382</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45085</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48391,7 +48391,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48567,7 +48567,7 @@
         <v>45258</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45617</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>45646</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48738,7 +48738,7 @@
         <v>45342</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48795,7 +48795,7 @@
         <v>45342</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48852,7 +48852,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48914,7 +48914,7 @@
         <v>45660</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48971,7 +48971,7 @@
         <v>44364</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49028,7 +49028,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49204,7 +49204,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49266,7 +49266,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>44944</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49380,7 +49380,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49494,7 +49494,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49551,7 +49551,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49670,7 +49670,7 @@
         <v>45180</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49727,7 +49727,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49784,7 +49784,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49841,7 +49841,7 @@
         <v>44371</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49898,7 +49898,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49955,7 +49955,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50012,7 +50012,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45758.52722222222</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50183,7 +50183,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50240,7 +50240,7 @@
         <v>45202</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50297,7 +50297,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>44488</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>45733</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45107</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45243</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50649,7 +50649,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50706,7 +50706,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45183</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45016</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45187.4346412037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>44454</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>44595</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45579</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45680</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>44818</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45761</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52441,7 +52441,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>44720</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>45461</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>45264</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45646</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>45212</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45366</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45450</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45540</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53420,7 +53420,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53477,7 +53477,7 @@
         <v>45107</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53539,7 +53539,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53596,7 +53596,7 @@
         <v>45239</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>45223</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53720,7 +53720,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>44880</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53891,7 +53891,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53948,7 +53948,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54067,7 +54067,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54124,7 +54124,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54186,7 +54186,7 @@
         <v>45091</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54243,7 +54243,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>45194</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54357,7 +54357,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45810</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45833</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44432</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>44382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44901</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>45548</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45692</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44813</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>44151</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44172</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44083</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>44270</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44217</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44203</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>44210</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44180</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44203</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44187</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44127</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44336</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44720</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44601</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44424</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44146</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44532</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>44084</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44729</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44572</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44188</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44224</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44153</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44460</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44151</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44208</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44152</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44186</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>44763</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44169</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44381</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44069.50508101852</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44347</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44854</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44200</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44859</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44517</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44517</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44147</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44153</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44153</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44127</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44389</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44153</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44147</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44125</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44326</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44603</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44103</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44839</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44083</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44148</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44650</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44119</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44452</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44279</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44105</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44295</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44438</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44365</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44799</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44299</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44488</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44722</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44370</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44522</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>44195</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44452</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44728</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44785.455</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44166</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44208</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44480</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44133</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44509</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44536</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44076</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44729</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44127</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44712</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44452</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44242</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44180</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44119</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44279</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44165</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44480</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44467</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44147</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44879</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44636</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45342</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44088</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44496</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44218</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45450</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45719</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44880</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44631</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44945</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44839</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45453</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44732</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45180</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44967</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44806</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45342</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45758.52722222222</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45223</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45643</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45016</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45107</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45257</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45239</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44595</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45097</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44364</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45043</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45680</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45415</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45091</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44805</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44187</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45548</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45243</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44720</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45219</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45366</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44967</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45251</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45299</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45123</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45761</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45176</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45208</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45448</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>44916</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45205</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45702</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44796</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45331</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44595</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45461</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44110</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>44671</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44895</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45016</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45779.64287037037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44151</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45540</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44370</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45428</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45534</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45453</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45428</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45187</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45161</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44371</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45733</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44076</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45212</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45786.59866898148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45264</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45212</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45104</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45110</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45793</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44151</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45366</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>44897</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44894</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>44162</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45461</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45240</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44620</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>44279</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45183</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>44662</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45796</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45485</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44137</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44381</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44862</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45219</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45229</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>44454</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45646</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>44791</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44267</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45799</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45194</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45800</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44133</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45405</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45607</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45097</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45747</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45107</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45155</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45246</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45238</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45085</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45547</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>44505</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45660</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45810</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45240</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45149</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44879</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45189</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45779</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44908</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45436</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45163</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44130</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44886</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44070</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45246</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45740</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45579</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44204</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>44239</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45310</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44818</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44830</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45008</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45114</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45827</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45366</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45827</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>44382</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44203</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45646</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45827</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>44840</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45827</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>44267</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>44515</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45545</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>44383</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45061</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45433</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>44167</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>44532</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45251</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45180</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44952</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45211</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44489</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45352</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45335</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45643</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45107</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45204</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45205</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45853</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45215</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45793</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>44594</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>44944</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45840</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45244</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45883.375</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45366</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45631</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>44883</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45882</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>45366</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45887.41885416667</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45887.40658564815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45887.38575231482</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45845</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45887.60866898148</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45737</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>44511</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>44526</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45887.60680555556</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45887.41712962963</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45617</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45888.63737268518</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>44488</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>44203</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45891.4975462963</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45891.63368055555</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45887</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45890.44188657407</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45848</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
         <v>45891.62481481482</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>45351</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45891.61936342593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>45149</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>44914</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>44160</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>44596</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>44239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45548</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>44161</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54233,7 +54233,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45016</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54347,7 +54347,7 @@
         <v>45016</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54518,7 +54518,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54575,7 +54575,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45810</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45833</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44432</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
         <v>44382</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44901</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1966,7 +1966,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>45548</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45692</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44813</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>44151</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44172</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44083</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>44270</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44217</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44203</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>44210</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44180</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44203</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44187</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44127</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44336</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44720</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44601</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44424</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44146</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44532</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>44084</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44729</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
         <v>44572</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44188</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44224</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44153</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44460</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44585</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44151</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44208</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44152</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44186</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>44763</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44169</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44381</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44069.50508101852</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44347</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7519,7 +7519,7 @@
         <v>44854</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7576,7 +7576,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44200</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>44859</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44517</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>44517</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44517</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44147</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44153</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44153</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>44127</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>44389</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>44153</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44147</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44125</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44326</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44603</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9083,7 +9083,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44103</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44839</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44083</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         <v>44148</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9487,7 +9487,7 @@
         <v>44650</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9601,7 +9601,7 @@
         <v>44119</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44452</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>44279</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44105</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44295</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44438</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44365</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44799</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44299</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44488</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44722</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44370</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44522</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         <v>44195</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>44452</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>44728</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         <v>44785.455</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>44166</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11232,7 +11232,7 @@
         <v>44208</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44480</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>44133</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44509</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11460,7 +11460,7 @@
         <v>44536</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>44076</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>44729</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44127</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44712</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44452</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>44242</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>44180</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>44119</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44279</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44165</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44480</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44467</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44147</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44879</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44636</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45342</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44088</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>44496</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13034,7 +13034,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
         <v>44218</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45450</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>44706</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45719</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>44880</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>44631</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44945</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44839</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14008,7 +14008,7 @@
         <v>45453</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14298,7 +14298,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>44732</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45180</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44967</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>44806</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45342</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45758.52722222222</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45223</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45643</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45016</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>45107</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45257</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45239</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44595</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16209,7 +16209,7 @@
         <v>45097</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>44364</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16380,7 +16380,7 @@
         <v>45043</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>45680</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>45415</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45091</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16846,7 +16846,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44805</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17022,7 +17022,7 @@
         <v>44187</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>45548</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17312,7 +17312,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
         <v>45243</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17426,7 +17426,7 @@
         <v>44720</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         <v>45219</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17711,7 +17711,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17825,7 +17825,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>45366</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>44967</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18224,7 +18224,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18343,7 +18343,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18514,7 +18514,7 @@
         <v>45251</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18685,7 +18685,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45299</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>45123</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45761</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19327,7 +19327,7 @@
         <v>45176</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45208</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45448</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>44916</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45205</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45702</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20311,7 +20311,7 @@
         <v>44796</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45331</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44595</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21124,7 +21124,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21466,7 +21466,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>45461</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44110</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45243</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>44671</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22160,7 +22160,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>44895</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22901,7 +22901,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45016</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45779.64287037037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44151</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45540</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44370</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24066,7 +24066,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45428</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45534</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24413,7 +24413,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45453</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45428</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45187</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45161</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44371</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45258</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45733</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>44076</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45212</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>45786.59866898148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45264</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45212</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45104</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45110</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27831,7 +27831,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27888,7 +27888,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28173,7 +28173,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>45793</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>44151</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45366</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28800,7 +28800,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>44897</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>44894</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29028,7 +29028,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29085,7 +29085,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29199,7 +29199,7 @@
         <v>44162</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29313,7 +29313,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>45461</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>45240</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29484,7 +29484,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>44620</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29712,7 +29712,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29769,7 +29769,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29826,7 +29826,7 @@
         <v>44279</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30064,7 +30064,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30121,7 +30121,7 @@
         <v>45222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30178,7 +30178,7 @@
         <v>45183</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30235,7 +30235,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>44662</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30520,7 +30520,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30577,7 +30577,7 @@
         <v>45796</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30691,7 +30691,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30748,7 +30748,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30862,7 +30862,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>45485</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -30976,7 +30976,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31090,7 +31090,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31147,7 +31147,7 @@
         <v>44137</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>44381</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31261,7 +31261,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31432,7 +31432,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>44862</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31603,7 +31603,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31717,7 +31717,7 @@
         <v>45219</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>44407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -31945,7 +31945,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45229</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32116,7 +32116,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32235,7 +32235,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32292,7 +32292,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32406,7 +32406,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>44454</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45646</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>44791</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44267</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>45799</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33328,7 +33328,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45194</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45800</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>44133</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -33980,7 +33980,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34037,7 +34037,7 @@
         <v>45405</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34094,7 +34094,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45607</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45097</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>45747</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35083,7 +35083,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45107</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45155</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45246</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45238</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45762</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36196,7 +36196,7 @@
         <v>45085</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>45547</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>44505</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>45660</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45810</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45240</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45149</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36781,7 +36781,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36952,7 +36952,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37009,7 +37009,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37066,7 +37066,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37180,7 +37180,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37237,7 +37237,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37294,7 +37294,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37832,7 +37832,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>44879</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45189</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45779</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38469,7 +38469,7 @@
         <v>44908</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>45436</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45163</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38816,7 +38816,7 @@
         <v>44130</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>44886</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44070</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39815,7 +39815,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39872,7 +39872,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39986,7 +39986,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45246</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45740</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45579</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40561,7 +40561,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44204</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40794,7 +40794,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40851,7 +40851,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40913,7 +40913,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40970,7 +40970,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41027,7 +41027,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41141,7 +41141,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>44239</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41369,7 +41369,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41431,7 +41431,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41488,7 +41488,7 @@
         <v>45310</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>44818</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>44830</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45008</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>45114</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41835,7 +41835,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41954,7 +41954,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42011,7 +42011,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42068,7 +42068,7 @@
         <v>45219</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>45219</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45827</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45366</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>45827</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>44382</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>44203</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42648,7 +42648,7 @@
         <v>45646</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42705,7 +42705,7 @@
         <v>45827</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42762,7 +42762,7 @@
         <v>44840</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42876,7 +42876,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42933,7 +42933,7 @@
         <v>45827</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42990,7 +42990,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43047,7 +43047,7 @@
         <v>44267</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43218,7 +43218,7 @@
         <v>44515</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43399,7 +43399,7 @@
         <v>45545</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43637,7 +43637,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43699,7 +43699,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43813,7 +43813,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43870,7 +43870,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>44383</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44051,7 +44051,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44108,7 +44108,7 @@
         <v>45061</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44165,7 +44165,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44222,7 +44222,7 @@
         <v>45433</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44398,7 +44398,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44455,7 +44455,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44512,7 +44512,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44569,7 +44569,7 @@
         <v>44167</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44626,7 +44626,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44683,7 +44683,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44797,7 +44797,7 @@
         <v>44532</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>45251</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45180</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44973,7 +44973,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45087,7 +45087,7 @@
         <v>44952</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45144,7 +45144,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45201,7 +45201,7 @@
         <v>45211</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45315,7 +45315,7 @@
         <v>44489</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45372,7 +45372,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45429,7 +45429,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45486,7 +45486,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45605,7 +45605,7 @@
         <v>45352</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>45335</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45643</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46061,7 +46061,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45107</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46361,7 +46361,7 @@
         <v>45204</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46418,7 +46418,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46480,7 +46480,7 @@
         <v>45205</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45202</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45853</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46713,7 +46713,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46770,7 +46770,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46884,7 +46884,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>45215</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46998,7 +46998,7 @@
         <v>45793</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47055,7 +47055,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>44594</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47288,7 +47288,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47350,7 +47350,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>44944</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47583,7 +47583,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47697,7 +47697,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47868,7 +47868,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47925,7 +47925,7 @@
         <v>45840</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45244</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45883.375</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>45366</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48671,7 +48671,7 @@
         <v>45631</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48728,7 +48728,7 @@
         <v>44883</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45882</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49194,7 +49194,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49308,7 +49308,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49546,7 +49546,7 @@
         <v>45366</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49603,7 +49603,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49660,7 +49660,7 @@
         <v>45887.41885416667</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49774,7 +49774,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45887.40658564815</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45887.38575231482</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49945,7 +49945,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50002,7 +50002,7 @@
         <v>45845</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50059,7 +50059,7 @@
         <v>45887.60866898148</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50116,7 +50116,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50230,7 +50230,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50287,7 +50287,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50344,7 +50344,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50401,7 +50401,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50463,7 +50463,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50520,7 +50520,7 @@
         <v>45737</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50577,7 +50577,7 @@
         <v>44511</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50639,7 +50639,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>44526</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50753,7 +50753,7 @@
         <v>45887.60680555556</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50929,7 +50929,7 @@
         <v>45887.41712962963</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51048,7 +51048,7 @@
         <v>45617</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51105,7 +51105,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45888.63737268518</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>44488</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51742,7 +51742,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51799,7 +51799,7 @@
         <v>44203</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51861,7 +51861,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51975,7 +51975,7 @@
         <v>45891.4975462963</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52032,7 +52032,7 @@
         <v>45891.63368055555</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45887</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>45890.44188657407</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>45848</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52265,7 +52265,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52322,7 +52322,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52379,7 +52379,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52498,7 +52498,7 @@
         <v>45891.62481481482</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52555,7 +52555,7 @@
         <v>45351</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52612,7 +52612,7 @@
         <v>45891.61936342593</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52669,7 +52669,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52726,7 +52726,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>45149</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52954,7 +52954,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53068,7 +53068,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>44914</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>44160</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>44596</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53472,7 +53472,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53534,7 +53534,7 @@
         <v>45205</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53591,7 +53591,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53710,7 +53710,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53767,7 +53767,7 @@
         <v>44239</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53824,7 +53824,7 @@
         <v>45548</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53943,7 +53943,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54062,7 +54062,7 @@
         <v>44161</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54233,7 +54233,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45016</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54347,7 +54347,7 @@
         <v>45016</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54404,7 +54404,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54518,7 +54518,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54575,7 +54575,7 @@
         <v>45169</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45810</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45833</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44813</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45548</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44901</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45692</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>44151</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44172</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>44083</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>44180</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44089</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>44270</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>44217</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44203</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>44210</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44180</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44203</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44187</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44127</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44336</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44720</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44601</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44424</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44146</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44532</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>44585</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44084</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44729</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44572</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44188</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44224</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44151</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44153</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44460</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44152</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44208</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44186</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>44763</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44169</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44381</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44347</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44854</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44859</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44517</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44517</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44517</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44147</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44153</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44153</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44127</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44389</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44153</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44147</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44125</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44148</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44083</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44452</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44119</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44650</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44105</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44365</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44279</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44295</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44799</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44299</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44438</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44370</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44488</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44796</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44722</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44195</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44522</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44728</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44785.455</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44208</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44452</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44536</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44076</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44127</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44509</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44166</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44480</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44452</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44133</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44729</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44165</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44467</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44147</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44242</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44180</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44088</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44119</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44218</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44279</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44636</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44879</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44496</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44326</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44103</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44839</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45251</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44603</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45405</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45107</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44267</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45240</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45335</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45366</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45548</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45219</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45258</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44945</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45352</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45243</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44895</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45104</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45299</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45428</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44151</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45163</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45453</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45187</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45428</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>44076</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45436</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44595</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45110</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45534</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45149</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45161</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45461</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45643</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45366</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45043</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44532</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44914</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45793</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44137</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45796</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44162</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44620</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44130</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45485</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44279</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44894</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44526</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44596</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45643</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45799</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44133</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45800</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45366</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44407</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44161</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45366</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44671</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45246</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45155</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45222</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45607</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45180</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45810</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44167</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45762</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44594</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45779</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45547</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45211</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45740</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45351</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45240</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44203</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45433</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44967</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>44203</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45827</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45205</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45701</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45827</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45208</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45827</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45827</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>44187</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45238</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45212</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45448</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45061</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44239</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45257</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44897</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44706</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>44791</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34890,7 +34890,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45415</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>44505</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45219</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45204</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45123</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45793</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45331</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>44952</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45246</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45205</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45882</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>45719</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>44631</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44489</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44511</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45883.375</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45149</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45887.40658564815</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45887.41885416667</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44806</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45887.60866898148</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45251</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45887.38575231482</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45887.60680555556</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45887.41712962963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45737</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>44840</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45888.63737268518</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45845</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45890.44188657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45848</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45702</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45453</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>44839</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45631</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45887</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44830</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45891.4975462963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45891.61936342593</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45894.60725694444</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45894.61140046296</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45169</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45114</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45891.62481481482</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45894.34238425926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45852</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44883</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45891.63368055555</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45895.46172453704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45853</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45896.6021875</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>44732</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45895.62541666667</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45895.4652199074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45244</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45897.43212962963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45898.40681712963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45898.42072916667</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45898.43726851852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45898.42881944445</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44796</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45894</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45898.54394675926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45897.43541666667</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44777,7 +44777,7 @@
         <v>45897.643125</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44948,7 +44948,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44110</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>44383</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44370</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>45545</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45548</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>44381</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>44382</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>44908</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45646</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45660</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>44862</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>44515</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>44364</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>44879</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>44204</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>44944</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45008</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>44239</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>44371</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>44805</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>44916</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>44160</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>44488</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45097</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45205</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>44662</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45016</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>44454</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>44886</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44595</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45016</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45761</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45229</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45223</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45264</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44967</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>45646</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>45097</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45107</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>45189</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45016</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45016</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>44267</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45219</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45310</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45215</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>45176</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45258</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45617</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52654,7 +52654,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>45180</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52768,7 +52768,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52939,7 +52939,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52996,7 +52996,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53053,7 +53053,7 @@
         <v>45202</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45733</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>45107</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45183</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53514,7 +53514,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45579</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53809,7 +53809,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>45680</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>44818</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54151,7 +54151,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>44720</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>45461</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45212</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45366</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45450</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45540</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>44880</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45091</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45194</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45810</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45833</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>44813</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45548</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44901</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45692</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>44151</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>44172</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>44083</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>44180</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44089</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>44270</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3179,7 +3179,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>44217</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44203</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>44210</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>44180</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44203</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44187</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44127</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4230,7 +4230,7 @@
         <v>44336</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>44720</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         <v>44601</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4401,7 +4401,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>44424</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4629,7 +4629,7 @@
         <v>44146</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44532</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>44585</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44084</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44729</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>44572</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>44188</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44224</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44151</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44153</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44078.56528935185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44460</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6240,7 +6240,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>44152</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44208</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6773,7 +6773,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44186</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>44763</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44169</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>44875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44381</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7343,7 +7343,7 @@
         <v>44347</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44854</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44209</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7747,7 +7747,7 @@
         <v>44859</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         <v>44517</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44517</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44517</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44147</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44153</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>44153</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44127</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>44389</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>44153</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44147</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>44125</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44148</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44083</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44452</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44119</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44650</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44105</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44365</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
         <v>44279</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>44295</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44799</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         <v>44299</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>44438</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44370</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9839,7 +9839,7 @@
         <v>44488</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44796</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44722</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>44195</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10067,7 +10067,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         <v>44522</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44728</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44785.455</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>44208</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44452</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>44536</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44076</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>44127</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>44509</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44166</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44480</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44452</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44133</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>44729</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44165</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>44480</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44467</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44147</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11579,7 +11579,7 @@
         <v>44712</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11636,7 +11636,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11693,7 +11693,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44242</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44180</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>44088</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>44119</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44218</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44279</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44636</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44879</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44496</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44326</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12630,7 +12630,7 @@
         <v>44103</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44839</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>45251</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45747</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12920,7 +12920,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44603</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13619,7 +13619,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13738,7 +13738,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13795,7 +13795,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13909,7 +13909,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45405</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45107</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44267</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45240</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14422,7 +14422,7 @@
         <v>45335</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45366</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>45548</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15111,7 +15111,7 @@
         <v>45219</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>45258</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44945</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45776.56582175926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>45352</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45243</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>44895</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45104</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45299</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16722,7 +16722,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45428</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44151</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17349,7 +17349,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45163</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17691,7 +17691,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45453</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45187</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45428</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>44076</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45436</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44595</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18898,7 +18898,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45110</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45534</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45149</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45161</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20021,7 +20021,7 @@
         <v>45461</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45643</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45366</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45043</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44532</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>44914</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>44151</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21461,7 +21461,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21803,7 +21803,7 @@
         <v>45793</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21860,7 +21860,7 @@
         <v>44137</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>45796</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22031,7 +22031,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44162</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22715,7 +22715,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44620</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44130</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>45485</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44279</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>44894</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44526</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>44596</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45643</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23818,7 +23818,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45799</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44133</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>45800</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45366</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44407</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>44161</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45366</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>44671</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45246</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45155</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26718,7 +26718,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26889,7 +26889,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45222</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>45607</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45180</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27345,7 +27345,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45810</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27640,7 +27640,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>44167</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27868,7 +27868,7 @@
         <v>45762</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28225,7 +28225,7 @@
         <v>44594</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28282,7 +28282,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28344,7 +28344,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28406,7 +28406,7 @@
         <v>45779</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45547</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>45211</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29375,7 +29375,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45740</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29732,7 +29732,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45351</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30312,7 +30312,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30369,7 +30369,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30726,7 +30726,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45240</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>44203</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45433</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44967</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>44203</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>45037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31611,7 +31611,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>45827</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32067,7 +32067,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32181,7 +32181,7 @@
         <v>45205</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32238,7 +32238,7 @@
         <v>45701</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32295,7 +32295,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>45827</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32466,7 +32466,7 @@
         <v>45208</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32523,7 +32523,7 @@
         <v>45827</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45827</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32756,7 +32756,7 @@
         <v>44187</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32813,7 +32813,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45238</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45212</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45448</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>45061</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>44239</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45257</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44897</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>44706</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34605,7 +34605,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34776,7 +34776,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>44791</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34890,7 +34890,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34947,7 +34947,7 @@
         <v>45415</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35061,7 +35061,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35118,7 +35118,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>44505</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45219</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>45204</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45123</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36117,7 +36117,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36231,7 +36231,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36702,7 +36702,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36997,7 +36997,7 @@
         <v>45793</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37054,7 +37054,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45331</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45840</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>44952</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45246</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37686,7 +37686,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37743,7 +37743,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37800,7 +37800,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>45205</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45882</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>45719</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>44631</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38370,7 +38370,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44489</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44511</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45883.375</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38950,7 +38950,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39007,7 +39007,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39126,7 +39126,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39183,7 +39183,7 @@
         <v>45149</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39297,7 +39297,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39354,7 +39354,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39411,7 +39411,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45887.40658564815</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45887.41885416667</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44806</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45887.60866898148</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45251</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45887.38575231482</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>45887.60680555556</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45887.41712962963</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40551,7 +40551,7 @@
         <v>45737</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>44840</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45888.63737268518</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45845</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>45890.44188657407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45848</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45702</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45453</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41592,7 +41592,7 @@
         <v>44839</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41706,7 +41706,7 @@
         <v>45631</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41763,7 +41763,7 @@
         <v>45887</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44830</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45891.4975462963</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42167,7 +42167,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42286,7 +42286,7 @@
         <v>45891.61936342593</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>45894.60725694444</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45894.61140046296</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45169</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>45114</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42628,7 +42628,7 @@
         <v>45891.62481481482</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42685,7 +42685,7 @@
         <v>45894.34238425926</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45852</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>44883</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45891.63368055555</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45895.46172453704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45853</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45896.6021875</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>44732</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>45895.62541666667</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45895.4652199074</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45244</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45897.43212962963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44026,7 +44026,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44145,7 +44145,7 @@
         <v>45898.40681712963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44202,7 +44202,7 @@
         <v>45898.42072916667</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44259,7 +44259,7 @@
         <v>45898.43726851852</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44316,7 +44316,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44373,7 +44373,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>45898.42881944445</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44796</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44606,7 +44606,7 @@
         <v>45894</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44663,7 +44663,7 @@
         <v>45898.54394675926</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>45897.43541666667</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44777,7 +44777,7 @@
         <v>45897.643125</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44891,7 +44891,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44948,7 +44948,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45010,7 +45010,7 @@
         <v>44110</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45067,7 +45067,7 @@
         <v>44383</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45129,7 +45129,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45243,7 +45243,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45300,7 +45300,7 @@
         <v>44370</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>45545</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45548</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>44381</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>44382</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45895,7 +45895,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45952,7 +45952,7 @@
         <v>44908</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45646</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46123,7 +46123,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>45660</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46237,7 +46237,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46294,7 +46294,7 @@
         <v>44862</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>44515</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>44364</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>44879</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46532,7 +46532,7 @@
         <v>44204</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46594,7 +46594,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>44944</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46708,7 +46708,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>45008</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>44239</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46936,7 +46936,7 @@
         <v>44371</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>44805</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47107,7 +47107,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47164,7 +47164,7 @@
         <v>44916</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47221,7 +47221,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47278,7 +47278,7 @@
         <v>44160</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47449,7 +47449,7 @@
         <v>44488</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47506,7 +47506,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47568,7 +47568,7 @@
         <v>45243</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47744,7 +47744,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47801,7 +47801,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45097</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>45205</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47972,7 +47972,7 @@
         <v>44662</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48029,7 +48029,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48086,7 +48086,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48143,7 +48143,7 @@
         <v>45016</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48200,7 +48200,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48257,7 +48257,7 @@
         <v>44454</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48428,7 +48428,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48485,7 +48485,7 @@
         <v>44886</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48547,7 +48547,7 @@
         <v>45219</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48604,7 +48604,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48718,7 +48718,7 @@
         <v>44595</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48775,7 +48775,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48889,7 +48889,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48946,7 +48946,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49003,7 +49003,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49060,7 +49060,7 @@
         <v>45016</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49174,7 +49174,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45761</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45229</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45223</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49526,7 +49526,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45264</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49640,7 +49640,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49697,7 +49697,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49754,7 +49754,7 @@
         <v>44967</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49811,7 +49811,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>45646</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49982,7 +49982,7 @@
         <v>45097</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50096,7 +50096,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50153,7 +50153,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50272,7 +50272,7 @@
         <v>45107</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50334,7 +50334,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50448,7 +50448,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50686,7 +50686,7 @@
         <v>45189</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50743,7 +50743,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50805,7 +50805,7 @@
         <v>45016</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50862,7 +50862,7 @@
         <v>45016</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50919,7 +50919,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50976,7 +50976,7 @@
         <v>44267</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51090,7 +51090,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51147,7 +51147,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51204,7 +51204,7 @@
         <v>45219</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>45310</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51323,7 +51323,7 @@
         <v>45215</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51380,7 +51380,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51437,7 +51437,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>45176</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51608,7 +51608,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51665,7 +51665,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51779,7 +51779,7 @@
         <v>45085</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45258</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45617</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>45342</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45342</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52245,7 +52245,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52302,7 +52302,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52421,7 +52421,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52535,7 +52535,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52592,7 +52592,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52654,7 +52654,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52711,7 +52711,7 @@
         <v>45180</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52768,7 +52768,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52882,7 +52882,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52939,7 +52939,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52996,7 +52996,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53053,7 +53053,7 @@
         <v>45202</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53110,7 +53110,7 @@
         <v>45733</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>45107</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53229,7 +53229,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53286,7 +53286,7 @@
         <v>45183</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53343,7 +53343,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53400,7 +53400,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53514,7 +53514,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53633,7 +53633,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53690,7 +53690,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53747,7 +53747,7 @@
         <v>45579</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53809,7 +53809,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53866,7 +53866,7 @@
         <v>45680</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>44818</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54094,7 +54094,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54151,7 +54151,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54208,7 +54208,7 @@
         <v>44720</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>45461</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54322,7 +54322,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54384,7 +54384,7 @@
         <v>45212</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54441,7 +54441,7 @@
         <v>45366</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54498,7 +54498,7 @@
         <v>45450</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54555,7 +54555,7 @@
         <v>45540</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54617,7 +54617,7 @@
         <v>45239</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54679,7 +54679,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54736,7 +54736,7 @@
         <v>44880</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54850,7 +54850,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54907,7 +54907,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54964,7 +54964,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55026,7 +55026,7 @@
         <v>45091</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55083,7 +55083,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45194</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>45810</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44081</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44881</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>45548</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>45902.35131944445</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>45692</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>44813</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>44901</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>44151</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2694,7 +2694,7 @@
         <v>44105</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2751,7 +2751,7 @@
         <v>44172</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44083</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>44180</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44089</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44270</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>44217</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>44176</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3554,7 +3554,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3730,7 +3730,7 @@
         <v>44194</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44203</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>44210</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>44180</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>44203</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>44517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>44187</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4258,7 +4258,7 @@
         <v>44720</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>44127</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44336</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>44601</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4486,7 +4486,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>44424</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>44146</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44532</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>44585</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>44084</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>44729</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>44572</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>44188</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44224</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44151</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44153</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44460</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44208</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>44152</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6687,7 +6687,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44186</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>44763</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44169</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44875</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44381</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44347</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>44209</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>44854</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>44859</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>44517</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44517</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>44517</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>44147</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>44153</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44153</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>44127</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>44389</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>44147</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>44125</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44148</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44452</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         <v>44279</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44365</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>44799</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>44299</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>44295</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44438</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>44488</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         <v>44796</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>44722</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>44370</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9691,7 +9691,7 @@
         <v>44195</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44522</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44785.455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44728</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>44208</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44536</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44127</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10276,7 +10276,7 @@
         <v>44452</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>44509</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44452</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>44165</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>44480</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10566,7 +10566,7 @@
         <v>44467</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44166</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44133</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44729</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>44480</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11089,7 +11089,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11146,7 +11146,7 @@
         <v>44712</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>44242</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44180</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44119</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11493,7 +11493,7 @@
         <v>44279</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44147</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11669,7 +11669,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>44326</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         <v>44879</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44088</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12026,7 +12026,7 @@
         <v>44103</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>44218</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>44636</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44083</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>44496</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12425,7 +12425,7 @@
         <v>44650</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12482,7 +12482,7 @@
         <v>45239</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44839</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45342</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45043</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>44119</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44105</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44187</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>44603</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45548</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45331</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14093,7 +14093,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14150,7 +14150,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14207,7 +14207,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>44595</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14378,7 +14378,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14435,7 +14435,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14492,7 +14492,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>44151</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45366</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>45428</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45534</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>44880</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>44945</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15813,7 +15813,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15870,7 +15870,7 @@
         <v>45453</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45428</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16098,7 +16098,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16331,7 +16331,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16388,7 +16388,7 @@
         <v>45299</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16559,7 +16559,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16730,7 +16730,7 @@
         <v>45187</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45208</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45453</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45180</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44967</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>45205</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>44671</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>44796</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18398,7 +18398,7 @@
         <v>45161</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>44370</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45643</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45037</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18993,7 +18993,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45107</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19169,7 +19169,7 @@
         <v>45257</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45461</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>44110</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45243</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19692,7 +19692,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19868,7 +19868,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44895</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20153,7 +20153,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45793</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>44371</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>45016</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21013,7 +21013,7 @@
         <v>44151</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21127,7 +21127,7 @@
         <v>45366</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>44894</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21355,7 +21355,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>44162</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21469,7 +21469,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21526,7 +21526,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21697,7 +21697,7 @@
         <v>44620</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21987,7 +21987,7 @@
         <v>44279</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45540</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45110</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45796</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45485</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23194,7 +23194,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>44137</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23308,7 +23308,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23365,7 +23365,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23484,7 +23484,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23598,7 +23598,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45258</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45733</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24007,7 +24007,7 @@
         <v>45222</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24121,7 +24121,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45183</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45212</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>44662</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24354,7 +24354,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45799</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45264</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>45212</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45104</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24986,7 +24986,7 @@
         <v>44381</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25100,7 +25100,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25157,7 +25157,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25395,7 +25395,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25457,7 +25457,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25576,7 +25576,7 @@
         <v>45800</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25638,7 +25638,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25695,7 +25695,7 @@
         <v>45219</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25876,7 +25876,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>44407</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>44897</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26451,7 +26451,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45461</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45240</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>44791</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26974,7 +26974,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27207,7 +27207,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27554,7 +27554,7 @@
         <v>45194</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>44133</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27725,7 +27725,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>44862</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45405</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45246</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45762</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45229</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45810</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28647,7 +28647,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28709,7 +28709,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44454</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>45646</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29698,7 +29698,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29755,7 +29755,7 @@
         <v>45155</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29869,7 +29869,7 @@
         <v>45238</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29983,7 +29983,7 @@
         <v>45547</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45701</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>45779</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45660</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44267</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31210,7 +31210,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         <v>45740</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31381,7 +31381,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31495,7 +31495,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31609,7 +31609,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31671,7 +31671,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31728,7 +31728,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>44879</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32080,7 +32080,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45189</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32313,7 +32313,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32427,7 +32427,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32541,7 +32541,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45827</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32655,7 +32655,7 @@
         <v>45827</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32712,7 +32712,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32769,7 +32769,7 @@
         <v>45827</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45827</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33054,7 +33054,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33111,7 +33111,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33287,7 +33287,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33344,7 +33344,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33401,7 +33401,7 @@
         <v>45874.61475694444</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45607</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45061</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33634,7 +33634,7 @@
         <v>45097</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45875.47131944444</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33810,7 +33810,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33867,7 +33867,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34038,7 +34038,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34209,7 +34209,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>45747</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34447,7 +34447,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34509,7 +34509,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>45205</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34628,7 +34628,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>44908</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34799,7 +34799,7 @@
         <v>45163</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>45793</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34913,7 +34913,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35032,7 +35032,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35322,7 +35322,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45840</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35493,7 +35493,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35550,7 +35550,7 @@
         <v>45883.375</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35669,7 +35669,7 @@
         <v>45882</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35783,7 +35783,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35840,7 +35840,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35897,7 +35897,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36135,7 +36135,7 @@
         <v>45107</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>45887.41885416667</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45887.40658564815</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45887.38575231482</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45845</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36596,7 +36596,7 @@
         <v>45887.60866898148</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36772,7 +36772,7 @@
         <v>45737</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36829,7 +36829,7 @@
         <v>45887.60680555556</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36886,7 +36886,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36948,7 +36948,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37062,7 +37062,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37119,7 +37119,7 @@
         <v>45887.41712962963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37352,7 +37352,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37409,7 +37409,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37466,7 +37466,7 @@
         <v>45888.63737268518</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37580,7 +37580,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37922,7 +37922,7 @@
         <v>45891.4975462963</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45891.63368055555</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38036,7 +38036,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45890.44188657407</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45848</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>45891.62481481482</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45891.61936342593</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45895.4652199074</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45894.60725694444</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>45852</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45246</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45894.34238425926</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45894.61140046296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45895.62541666667</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38844,7 +38844,7 @@
         <v>45085</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38901,7 +38901,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45887</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45853</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45895.46172453704</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39253,7 +39253,7 @@
         <v>45897.43212962963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39310,7 +39310,7 @@
         <v>45897.643125</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39367,7 +39367,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45896.6021875</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45897.43541666667</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>44505</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45898.43726851852</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>45898.54394675926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45898.42072916667</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>45898</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45901.34625</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>45579</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>45901.52376157408</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45898.42881944445</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40190,7 +40190,7 @@
         <v>45902.34259259259</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44153</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40304,7 +40304,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45894</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40418,7 +40418,7 @@
         <v>44204</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40537,7 +40537,7 @@
         <v>45240</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40594,7 +40594,7 @@
         <v>45149</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>45905.43700231481</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40822,7 +40822,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40879,7 +40879,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40936,7 +40936,7 @@
         <v>45904</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40993,7 +40993,7 @@
         <v>45310</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41055,7 +41055,7 @@
         <v>44818</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41169,7 +41169,7 @@
         <v>45008</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45114</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41340,7 +41340,7 @@
         <v>45905.54534722222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41454,7 +41454,7 @@
         <v>45904</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>45905.54412037037</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41630,7 +41630,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45905.46831018518</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41801,7 +41801,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41858,7 +41858,7 @@
         <v>44203</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41920,7 +41920,7 @@
         <v>45646</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>44840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42034,7 +42034,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>45904</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45436</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42210,7 +42210,7 @@
         <v>45545</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42386,7 +42386,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42443,7 +42443,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42505,7 +42505,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42624,7 +42624,7 @@
         <v>44130</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>44886</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>44167</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44532</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43204,7 +43204,7 @@
         <v>45251</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>44952</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43318,7 +43318,7 @@
         <v>44239</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>44489</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43432,7 +43432,7 @@
         <v>44830</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43546,7 +43546,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45352</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45219</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45219</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45366</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>44382</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>45107</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44183,7 +44183,7 @@
         <v>44267</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>44515</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44359,7 +44359,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>44383</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>45433</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44763,7 +44763,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44820,7 +44820,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44939,7 +44939,7 @@
         <v>45202</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44996,7 +44996,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>45180</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45167,7 +45167,7 @@
         <v>45211</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45258</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45457,7 +45457,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45809,7 +45809,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45866,7 +45866,7 @@
         <v>45366</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45923,7 +45923,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45980,7 +45980,7 @@
         <v>45335</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46037,7 +46037,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46151,7 +46151,7 @@
         <v>45643</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46322,7 +46322,7 @@
         <v>45204</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46436,7 +46436,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46550,7 +46550,7 @@
         <v>45215</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46607,7 +46607,7 @@
         <v>45366</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>44594</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>44944</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44511</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47125,7 +47125,7 @@
         <v>45617</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45244</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>45631</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>44883</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>44488</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47814,7 +47814,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47876,7 +47876,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47938,7 +47938,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48109,7 +48109,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48228,7 +48228,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48290,7 +48290,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48347,7 +48347,7 @@
         <v>44526</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48404,7 +48404,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48461,7 +48461,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>45149</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48637,7 +48637,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48694,7 +48694,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48751,7 +48751,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48808,7 +48808,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>44160</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48927,7 +48927,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>44203</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45205</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45351</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45548</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49574,7 +49574,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49631,7 +49631,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45016</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45016</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>44914</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45450</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50144,7 +50144,7 @@
         <v>44596</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45719</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>44839</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50719,7 +50719,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50776,7 +50776,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50833,7 +50833,7 @@
         <v>44239</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50890,7 +50890,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50947,7 +50947,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51009,7 +51009,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51066,7 +51066,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51123,7 +51123,7 @@
         <v>44161</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51237,7 +51237,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51294,7 +51294,7 @@
         <v>45342</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51351,7 +51351,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51465,7 +51465,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51579,7 +51579,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51636,7 +51636,7 @@
         <v>45016</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51693,7 +51693,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45169</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51807,7 +51807,7 @@
         <v>44706</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>45097</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>44631</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52035,7 +52035,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>44364</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52149,7 +52149,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>44732</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>44806</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52325,7 +52325,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52501,7 +52501,7 @@
         <v>45223</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>44967</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52672,7 +52672,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52729,7 +52729,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52791,7 +52791,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52848,7 +52848,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52962,7 +52962,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -53019,7 +53019,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53076,7 +53076,7 @@
         <v>44595</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53133,7 +53133,7 @@
         <v>45123</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53247,7 +53247,7 @@
         <v>45680</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53304,7 +53304,7 @@
         <v>45176</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53361,7 +53361,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53480,7 +53480,7 @@
         <v>45415</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>45091</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53594,7 +53594,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53713,7 +53713,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53770,7 +53770,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53832,7 +53832,7 @@
         <v>45448</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>44805</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53946,7 +53946,7 @@
         <v>44916</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45702</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54060,7 +54060,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54117,7 +54117,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54174,7 +54174,7 @@
         <v>45243</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54231,7 +54231,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54350,7 +54350,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54412,7 +54412,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>44720</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54526,7 +54526,7 @@
         <v>45219</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54640,7 +54640,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54754,7 +54754,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54873,7 +54873,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54930,7 +54930,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54987,7 +54987,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55044,7 +55044,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55101,7 +55101,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55158,7 +55158,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>45251</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55272,7 +55272,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55329,7 +55329,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55391,7 +55391,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55448,7 +55448,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55510,7 +55510,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55567,7 +55567,7 @@
         <v>45761</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55629,7 +55629,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>45810</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44881</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44813</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45548</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>44901</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45902.35131944445</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45692</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44151</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44172</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44180</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44089</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44270</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44176</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44217</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44203</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44210</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>44180</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44203</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44127</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44336</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44187</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44720</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44601</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44424</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44146</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44532</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44585</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44729</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44572</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44188</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44224</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44151</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44153</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44460</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44152</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44186</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44763</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44169</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44875</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44381</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44347</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44854</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44209</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44200</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44859</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44517</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44517</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44517</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44147</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44153</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44153</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44127</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44389</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44147</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44125</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44119</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44105</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44799</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44299</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44365</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44650</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44370</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44522</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44279</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44728</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44295</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44438</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44195</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44166</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44785.455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44208</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44488</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44133</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44536</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44127</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44452</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44509</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44722</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44712</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44729</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44165</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44242</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44180</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44480</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44467</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44119</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44147</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44279</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44088</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44218</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44326</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44452</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44103</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45335</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45251</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>45747</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45405</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44480</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44267</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44603</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45366</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45219</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45107</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45240</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45548</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45258</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44945</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45243</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44895</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45104</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45299</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45352</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45163</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45428</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44151</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45453</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45187</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44595</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45436</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45428</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45149</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45110</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45534</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45461</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45643</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45043</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45161</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44532</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45366</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44914</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44636</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44496</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44151</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>45793</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>44137</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45796</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44596</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44130</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44162</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44620</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45643</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45485</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44526</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44279</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44894</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45366</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45799</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44133</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44161</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44839</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44671</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45800</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45607</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45180</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>44167</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45366</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45246</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45547</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45155</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45211</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44594</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45810</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45762</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45240</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>44203</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45433</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45779</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45205</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45208</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45238</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45740</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>44791</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>44967</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>44203</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45827</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45219</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45204</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45827</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45827</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45827</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>44187</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45331</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45061</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>45246</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45212</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45448</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45719</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>44239</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45257</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44897</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44706</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45415</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>44505</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45123</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45149</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44952</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45251</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>44489</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44511</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>44840</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45793</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45840</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45453</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45702</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44839</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45631</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44830</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45114</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>44883</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44796</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>44110</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>44383</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45883.375</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>44732</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>44370</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45545</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44381</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44382</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45244</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45646</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45660</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>44364</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>44371</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>45775.59769675926</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45471.43636574074</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42031,7 +42031,7 @@
         <v>44526.37672453704</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42088,7 +42088,7 @@
         <v>44831.59701388889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>45700.63662037037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>45841.63774305556</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -42259,7 +42259,7 @@
         <v>45841.64856481482</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>44488</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -42373,7 +42373,7 @@
         <v>45243</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45527.32589120371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45721.42768518518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -42549,7 +42549,7 @@
         <v>45748.40988425926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -42606,7 +42606,7 @@
         <v>45747.3884375</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -42663,7 +42663,7 @@
         <v>44596.5728125</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -42720,7 +42720,7 @@
         <v>45568.44828703703</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45016</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -42834,7 +42834,7 @@
         <v>45057.62391203704</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>44454</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -42948,7 +42948,7 @@
         <v>45841.65119212963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>45040.57412037037</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>44573.50443287037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43119,7 +43119,7 @@
         <v>44595</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43176,7 +43176,7 @@
         <v>45841.63111111111</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -43233,7 +43233,7 @@
         <v>45755.37341435185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>44855.65891203703</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45471.6062962963</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>45887.40658564815</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -43461,7 +43461,7 @@
         <v>45887.41885416667</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>45733.62225694444</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -43575,7 +43575,7 @@
         <v>45887.60866898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -43632,7 +43632,7 @@
         <v>45846.5946412037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -43689,7 +43689,7 @@
         <v>45425.44804398148</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -43746,7 +43746,7 @@
         <v>45757.35046296296</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -43803,7 +43803,7 @@
         <v>44714.4553125</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45845.63385416667</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45414.63744212963</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45761</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44041,7 +44041,7 @@
         <v>45887.38575231482</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>44735.58756944445</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44155,7 +44155,7 @@
         <v>45733.36315972222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44212,7 +44212,7 @@
         <v>45548</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -44274,7 +44274,7 @@
         <v>45264</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -44331,7 +44331,7 @@
         <v>44802.5419675926</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>45646</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -44445,7 +44445,7 @@
         <v>45740.629375</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -44502,7 +44502,7 @@
         <v>45887.60680555556</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -44559,7 +44559,7 @@
         <v>45099.53201388889</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -44616,7 +44616,7 @@
         <v>45887.41712962963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>44908</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45845.64680555555</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>44594.32063657408</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -44844,7 +44844,7 @@
         <v>44872.42103009259</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -44901,7 +44901,7 @@
         <v>45548.55346064815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -44958,7 +44958,7 @@
         <v>45107</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>45845.65662037037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45077,7 +45077,7 @@
         <v>45737</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45134,7 +45134,7 @@
         <v>45845.67314814815</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>45555.55221064815</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>45492.92834490741</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>45542.70951388889</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -45362,7 +45362,7 @@
         <v>45888.63737268518</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>44862</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -45476,7 +45476,7 @@
         <v>44515</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>45845</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44879</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>44204</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -45719,7 +45719,7 @@
         <v>45555.49383101852</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>45008</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -45833,7 +45833,7 @@
         <v>45847.5684375</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -45890,7 +45890,7 @@
         <v>45890.44188657407</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -45947,7 +45947,7 @@
         <v>45848</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46009,7 +46009,7 @@
         <v>45761.34462962963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46071,7 +46071,7 @@
         <v>45847.57548611111</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>45099.66478009259</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46185,7 +46185,7 @@
         <v>44239</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>44805</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -46299,7 +46299,7 @@
         <v>45847.46365740741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -46356,7 +46356,7 @@
         <v>45176.41961805556</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>45847.37819444444</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -46470,7 +46470,7 @@
         <v>44916</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -46527,7 +46527,7 @@
         <v>44967.4797337963</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -46584,7 +46584,7 @@
         <v>45887</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -46641,7 +46641,7 @@
         <v>45852.5432175926</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -46703,7 +46703,7 @@
         <v>45891.61936342593</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>44160</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -46817,7 +46817,7 @@
         <v>45894.34238425926</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -46874,7 +46874,7 @@
         <v>45852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -46931,7 +46931,7 @@
         <v>45586.29105324074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>45895.46172453704</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47050,7 +47050,7 @@
         <v>45853</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>45896.6021875</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47169,7 +47169,7 @@
         <v>45097</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>45895.4652199074</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -47283,7 +47283,7 @@
         <v>45897.43212962963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>45855.54505787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -47402,7 +47402,7 @@
         <v>45205</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -47459,7 +47459,7 @@
         <v>44662</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -47516,7 +47516,7 @@
         <v>45155.66672453703</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -47573,7 +47573,7 @@
         <v>45898.42072916667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45898.43726851852</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>45855.3087962963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -47749,7 +47749,7 @@
         <v>45898.42881944445</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -47806,7 +47806,7 @@
         <v>44543.37199074074</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>45420.60313657407</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>44886</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -47982,7 +47982,7 @@
         <v>45219</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48039,7 +48039,7 @@
         <v>45727.8137037037</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48096,7 +48096,7 @@
         <v>45476.58725694445</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48153,7 +48153,7 @@
         <v>45898.54394675926</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48210,7 +48210,7 @@
         <v>45897.43541666667</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -48267,7 +48267,7 @@
         <v>45897.643125</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -48324,7 +48324,7 @@
         <v>45901.52376157408</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -48381,7 +48381,7 @@
         <v>45754.35082175926</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45902.34259259259</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -48495,7 +48495,7 @@
         <v>44153</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -48552,7 +48552,7 @@
         <v>45607.67049768518</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45016</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -48666,7 +48666,7 @@
         <v>45422.56760416667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>45901.34625</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45898</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -48842,7 +48842,7 @@
         <v>45229</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45223</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -48956,7 +48956,7 @@
         <v>45904</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>45460.40803240741</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49070,7 +49070,7 @@
         <v>44967</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49127,7 +49127,7 @@
         <v>44490.41263888889</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>45729.45688657407</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>45097</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>45904</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>45905.46831018518</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45908</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>45735.2934837963</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45597.84851851852</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45905.54412037037</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45908.35690972222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45905.54534722222</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45905.43700231481</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>45908.27134259259</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -49873,7 +49873,7 @@
         <v>44750.61899305556</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -49935,7 +49935,7 @@
         <v>45867.53563657407</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -49992,7 +49992,7 @@
         <v>45637.58819444444</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -50049,7 +50049,7 @@
         <v>45189</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>45867.54785879629</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -50163,7 +50163,7 @@
         <v>45867.61561342593</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>45867.5446875</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45145.58690972222</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -50339,7 +50339,7 @@
         <v>45016</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45016</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>45583.4724074074</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -50510,7 +50510,7 @@
         <v>44267</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45555.5541087963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -50624,7 +50624,7 @@
         <v>45555.55648148148</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -50681,7 +50681,7 @@
         <v>45891</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>45891</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -50795,7 +50795,7 @@
         <v>45869.4811574074</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45145.42189814815</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45912.57952546296</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -50966,7 +50966,7 @@
         <v>45912.63606481482</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>45912.63609953703</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -51080,7 +51080,7 @@
         <v>45904</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>45870.58332175926</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>45891</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45869.48569444445</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -51308,7 +51308,7 @@
         <v>45894</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -51365,7 +51365,7 @@
         <v>45869.5053587963</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -51422,7 +51422,7 @@
         <v>45912.32010416667</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -51479,7 +51479,7 @@
         <v>45894</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -51536,7 +51536,7 @@
         <v>45894</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -51593,7 +51593,7 @@
         <v>45219</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -51650,7 +51650,7 @@
         <v>45875</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>45874</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -51774,7 +51774,7 @@
         <v>45310</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45895</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -51893,7 +51893,7 @@
         <v>45215</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -51950,7 +51950,7 @@
         <v>45217.35626157407</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>45310.581875</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -52064,7 +52064,7 @@
         <v>45176</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>44886.48644675926</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -52178,7 +52178,7 @@
         <v>44865.47443287037</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45153.53344907407</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -52292,7 +52292,7 @@
         <v>45153.63834490741</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -52349,7 +52349,7 @@
         <v>45085</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -52406,7 +52406,7 @@
         <v>45587.63690972222</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>45258</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -52520,7 +52520,7 @@
         <v>45617</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45342</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>45342</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -52691,7 +52691,7 @@
         <v>45744.30840277778</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -52753,7 +52753,7 @@
         <v>45481.66096064815</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -52815,7 +52815,7 @@
         <v>45377.36298611111</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -52872,7 +52872,7 @@
         <v>45364.56289351852</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -52929,7 +52929,7 @@
         <v>45516.64608796296</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>45583.3762037037</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -53048,7 +53048,7 @@
         <v>44242.59861111111</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -53105,7 +53105,7 @@
         <v>45180.45332175926</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45757.29439814815</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -53224,7 +53224,7 @@
         <v>45622.56936342592</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>45180</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>45679.58766203704</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -53395,7 +53395,7 @@
         <v>44915.55640046296</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -53452,7 +53452,7 @@
         <v>45673.42638888889</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45673.43484953704</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -53566,7 +53566,7 @@
         <v>44714.71814814815</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -53623,7 +53623,7 @@
         <v>45202</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -53680,7 +53680,7 @@
         <v>45733</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -53737,7 +53737,7 @@
         <v>45107</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -53799,7 +53799,7 @@
         <v>45366.96065972222</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -53856,7 +53856,7 @@
         <v>45183</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -53913,7 +53913,7 @@
         <v>44298.51025462963</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -53970,7 +53970,7 @@
         <v>44749.65016203704</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -54027,7 +54027,7 @@
         <v>45232.61173611111</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45664.58971064815</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45252.5525462963</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -54203,7 +54203,7 @@
         <v>45649.45278935185</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>45643.5507175926</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>45579</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -54379,7 +54379,7 @@
         <v>45205.58381944444</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -54436,7 +54436,7 @@
         <v>45680</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -54493,7 +54493,7 @@
         <v>44818</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -54550,7 +54550,7 @@
         <v>45203.64033564815</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -54607,7 +54607,7 @@
         <v>45632.62980324074</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -54664,7 +54664,7 @@
         <v>45278.50369212963</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -54721,7 +54721,7 @@
         <v>45278.50765046296</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>44720</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -54835,7 +54835,7 @@
         <v>45461</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -54892,7 +54892,7 @@
         <v>45723.44689814815</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>45212</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -55011,7 +55011,7 @@
         <v>45366</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>45450</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>45540</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -55187,7 +55187,7 @@
         <v>45239</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>45629.68421296297</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -55306,7 +55306,7 @@
         <v>44880</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -55363,7 +55363,7 @@
         <v>45448.65388888889</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -55420,7 +55420,7 @@
         <v>45716.37329861111</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -55477,7 +55477,7 @@
         <v>45377.8671412037</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -55534,7 +55534,7 @@
         <v>45478.61469907407</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>45091</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -55653,7 +55653,7 @@
         <v>45644.55494212963</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -55710,7 +55710,7 @@
         <v>45194</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -55767,7 +55767,7 @@
         <v>45733.65908564815</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>

--- a/Översikt BOLLNÄS.xlsx
+++ b/Översikt BOLLNÄS.xlsx
@@ -567,7 +567,7 @@
         <v>44109</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44095</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>45833</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>45810</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44333.65168981482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>44432</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>44382</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>44488.65100694444</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         <v>45076</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>45058</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45471.40319444444</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>44881</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>44813</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>45548</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>45772.38952546296</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>44901</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
         <v>44714.65887731482</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>45525.59913194444</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45733.62414351852</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45902.35131944445</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>45692</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>44151</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44876.37364583334</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>44105</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44172</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>44314.2571875</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>44314.26172453703</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2832,7 +2832,7 @@
         <v>44314.26922453703</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>44180</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>44089</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>44270</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>44596.57570601852</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>44566.62109953703</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>44176</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>44217</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>44319.43662037037</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44785.39850694445</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>44830.40199074074</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44566.5825</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>44432.48314814815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>44203</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>44194</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>44210</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>44180</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>44203</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -3883,7 +3883,7 @@
         <v>44517.75414351852</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>44127</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>44517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4054,7 +4054,7 @@
         <v>44336</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>44488.65658564815</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>44187</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>44720</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44601</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>44616.60581018519</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44424</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>44441.54539351852</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>44784.71929398148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44146</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         <v>44488.65960648148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>44532</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -4743,7 +4743,7 @@
         <v>44585</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>44729</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>44572</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>44603.60409722223</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44603.60658564815</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
         <v>44603.6125925926</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44314.26796296296</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44697.25298611111</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44375.47541666667</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>44314.57642361111</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>44301.56144675926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44188</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44224</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>44090.48449074074</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>44151</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>44266.68041666667</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44153</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -5722,7 +5722,7 @@
         <v>44796.62805555556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44460</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>44538.44221064815</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44603.61780092592</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         <v>44659.36878472222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44672.65672453704</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44886.37402777778</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>44467.35965277778</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         <v>44152</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44566.60619212963</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44851.94770833333</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>44882.53259259259</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44243.60890046296</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         <v>44882.82246527778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44868.31685185185</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -6654,7 +6654,7 @@
         <v>44186</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44645.52770833333</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>44691.62394675926</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         <v>44299.64576388889</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>44676.44880787037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44763</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44169</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>44875</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>44381</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -7167,7 +7167,7 @@
         <v>44347</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44831.34217592593</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         <v>44854</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44209</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44200</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         <v>44106.46587962963</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44452.45461805556</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -7571,7 +7571,7 @@
         <v>44859</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44517</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -7685,7 +7685,7 @@
         <v>44517</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44517</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>44147</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>44153</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -7913,7 +7913,7 @@
         <v>44153</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>44127</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8032,7 +8032,7 @@
         <v>44369.69809027778</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         <v>44389</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44645.53327546296</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44645.53493055556</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -8265,7 +8265,7 @@
         <v>44511.92282407408</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>44147</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>44480.46203703704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44771.48913194444</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         <v>44125</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44481.36178240741</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         <v>44148</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>44119</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>44105</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44452</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>44757.508125</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -8907,7 +8907,7 @@
         <v>44799</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -8964,7 +8964,7 @@
         <v>44299</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44487.53695601852</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>44365</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         <v>44333.30881944444</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>44650</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         <v>44732.92746527777</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>44370</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         <v>44369.70108796296</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>44522</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         <v>44279</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44728</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>44295</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44438</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>44195</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>44263.6728125</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -9844,7 +9844,7 @@
         <v>44166</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>44785.455</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -9958,7 +9958,7 @@
         <v>44515.32060185185</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>44208</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44645.52859953704</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44488</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>44796</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44321.61015046296</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>44375.6319212963</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -10362,7 +10362,7 @@
         <v>44133</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>44536</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>44127</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44452</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44509</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>44722</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>44505.66327546296</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44729.44290509259</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>44712</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>44729</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>44706.34857638889</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>44165</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44242</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11108,7 +11108,7 @@
         <v>44180</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>44480</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44467</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44119</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -11351,7 +11351,7 @@
         <v>44686.56325231482</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44147</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -11465,7 +11465,7 @@
         <v>44279</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44483.4696875</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44872.38538194444</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>44879</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44735.5850462963</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44088</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>44831.60743055555</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44218.42019675926</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44218</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44326</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44452</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44103</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>45041.59797453704</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45335</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>45335.59482638889</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45174.54631944445</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45251</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>45747</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>45720.3500462963</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>45729.45340277778</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45232.56831018518</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>45219.33283564815</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>45774.49193287037</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>45743.43662037037</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45219.4821875</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         <v>45405</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>44333.43928240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>45212.43078703704</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>44480</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -13153,7 +13153,7 @@
         <v>44267</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>44603</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44603.58001157407</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>44603.59678240741</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45232.56078703704</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -13438,7 +13438,7 @@
         <v>45734.35393518519</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45092.28179398148</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>45092.57606481481</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45366</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45219</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>44620.60839120371</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45677.27112268518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>45526.41092592593</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>45183.32864583333</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45581.45340277778</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>44532.40591435185</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14075,7 +14075,7 @@
         <v>45582.39152777778</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45453.55662037037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45107</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -14246,7 +14246,7 @@
         <v>45639.25746527778</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45609.84217592593</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45240</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45716.36666666667</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45629.67824074074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>45530.47582175926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>45548</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -14650,7 +14650,7 @@
         <v>45258</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>45636.44435185185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -14764,7 +14764,7 @@
         <v>45672.4428125</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>44945</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         <v>45243</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -14935,7 +14935,7 @@
         <v>44895</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>45638.32483796297</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44999.58185185185</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>45110.42435185185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45104</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -15220,7 +15220,7 @@
         <v>45145.42378472222</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>44858.00943287037</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45755.36678240741</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>45574.54673611111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -15453,7 +15453,7 @@
         <v>45776.48444444445</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>45299</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>45352</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         <v>45776.48524305555</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45386.34846064815</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -15738,7 +15738,7 @@
         <v>45776.48304398148</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45457.53640046297</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -15852,7 +15852,7 @@
         <v>44509.43005787037</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45358.60657407407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45748.4383912037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16023,7 +16023,7 @@
         <v>45748.44193287037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45748.46032407408</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>45782.69534722222</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -16199,7 +16199,7 @@
         <v>45782.48126157407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -16256,7 +16256,7 @@
         <v>45107.48931712963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -16313,7 +16313,7 @@
         <v>45145.59108796297</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44580.4372337963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45782.41087962963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>45149.46030092592</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>45455.43077546296</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>45163</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -16660,7 +16660,7 @@
         <v>45428</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -16717,7 +16717,7 @@
         <v>44151</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>45500.43938657407</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>45434.70263888889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45583.54946759259</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45565.65407407407</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>45565.65543981481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>45555.5937962963</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45784.38891203704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -17173,7 +17173,7 @@
         <v>45583.54844907407</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -17230,7 +17230,7 @@
         <v>45453</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         <v>45579.66521990741</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45590.4315162037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45476.59189814814</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -17458,7 +17458,7 @@
         <v>45187</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>45261.61160879629</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45560.65509259259</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>44595</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45436</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -17748,7 +17748,7 @@
         <v>45506.33875</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -17810,7 +17810,7 @@
         <v>45506.34412037037</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45624.61965277778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45610.48736111111</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>45428</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45475.43817129629</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>45455.44559027778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45149</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45510.39796296296</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>44543.40311342593</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>45113.32282407407</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>45573.62100694444</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>44856.96982638889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45785.54400462963</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45506.62546296296</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>44914.56515046296</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45110</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45390.40768518519</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45565.58790509259</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44839.39199074074</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -18908,7 +18908,7 @@
         <v>45086.51684027778</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>45310.5827662037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>45534</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19084,7 +19084,7 @@
         <v>45692.37174768518</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45555.50454861111</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>45461</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45468.26278935185</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -19322,7 +19322,7 @@
         <v>45643</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45471.40547453704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>45583.46032407408</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45043</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45443.57775462963</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45161</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45790.4482175926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44532</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45786.60678240741</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>45789.43271990741</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -19912,7 +19912,7 @@
         <v>45533.32619212963</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45366</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>44914</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20088,7 +20088,7 @@
         <v>45460.66289351852</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>44859.44630787037</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45453.54730324074</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>44645.53158564815</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -20316,7 +20316,7 @@
         <v>45145.41471064815</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45213.37230324074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44636</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>45792.45871527777</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>44496</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>45792.35361111111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -20658,7 +20658,7 @@
         <v>45792.45457175926</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45709.55436342592</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45623.61159722223</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -20829,7 +20829,7 @@
         <v>45153.65484953704</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45471.56072916667</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>45758.52517361111</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45315.59603009259</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>45792.35172453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21114,7 +21114,7 @@
         <v>44151</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45583.54359953704</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -21228,7 +21228,7 @@
         <v>44886.46003472222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45433.75060185185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45497.28164351852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45497.28234953704</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -21456,7 +21456,7 @@
         <v>45796.40662037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45414.639375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>45793</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>44137</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45793.71438657407</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45796</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45796.64568287037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45793.72311342593</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45546.65759259259</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45485.36784722222</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45506.43253472223</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44596</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45793.69190972222</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>44130</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45588.62625</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>44162</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45478.63699074074</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45490.27436342592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>44620</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45643</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45485</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45795.6452662037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45733.61204861111</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>45733.67521990741</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>44526</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44279</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45590.47798611111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45566.28908564815</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45566.29006944445</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>45588.87435185185</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>44894</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45555.32482638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45558.64020833333</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45366</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>45470.93087962963</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -23471,7 +23471,7 @@
         <v>44886.469375</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -23528,7 +23528,7 @@
         <v>45439.44590277778</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -23585,7 +23585,7 @@
         <v>45701.61202546296</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45635.71362268519</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>45797.52796296297</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45797.55027777778</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>44531.56668981481</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>45799.54648148148</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -23932,7 +23932,7 @@
         <v>45799.55019675926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>45500.42336805556</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45800.48112268518</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24108,7 +24108,7 @@
         <v>45478.47041666666</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45799</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -24227,7 +24227,7 @@
         <v>44133</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>44161</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44839</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>45485.35292824074</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>44656.65101851852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>44622.40689814815</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>45800.50966435186</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45800.4756712963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -24688,7 +24688,7 @@
         <v>45800.45829861111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44671</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45727.3865162037</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45727.43175925926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>45119.55945601852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45799.55748842593</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25045,7 +25045,7 @@
         <v>44686.5978125</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45599.98630787037</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>45800</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45642.47278935185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>44816.56690972222</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44678.68134259259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>45667.43208333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>45475.54844907407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45803.52922453704</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>44910.60543981481</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45803.86391203704</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>45222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>45567.60054398148</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44407</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45804.64680555555</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -25910,7 +25910,7 @@
         <v>45607</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45180</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45804.37753472223</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26086,7 +26086,7 @@
         <v>45681.37418981481</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26143,7 +26143,7 @@
         <v>45805.62409722222</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45194.68771990741</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45161.61159722223</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45729.25450231481</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>44167</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45621.35841435185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45805.64973379629</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45805.66572916666</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45058.5878125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45672.47560185185</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45366</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45805.64239583333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45624.28030092592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45246</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45547</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45525.97503472222</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45155</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45771.37157407407</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>45211</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45664.56732638889</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>45664.60994212963</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45677.27587962963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45675.58435185185</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45810.35309027778</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>45524.58820601852</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45810.60430555556</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45810.49068287037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45351</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>45810.61306712963</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44594</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45810</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -27925,7 +27925,7 @@
         <v>45096.52631944444</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45812.64255787037</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45729.28755787037</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28101,7 +28101,7 @@
         <v>45639.27597222223</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45519.50747685185</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45812.62276620371</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45812.42059027778</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45762</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>45812.64680555555</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45540.53148148148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45692.58184027778</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45692.58333333334</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45812.28103009259</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>44616.92188657408</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45442.43586805555</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45240</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45702.36628472222</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>44203</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>45433</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45560.57263888889</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29095,7 +29095,7 @@
         <v>45572.53714120371</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45364.56001157407</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>45364.56122685185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45779</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -29323,7 +29323,7 @@
         <v>45205</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -29380,7 +29380,7 @@
         <v>45818.67405092593</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -29437,7 +29437,7 @@
         <v>45208</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45774.50434027778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -29556,7 +29556,7 @@
         <v>45818.66855324074</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -29613,7 +29613,7 @@
         <v>45230.36850694445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>45818.66342592592</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45238</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45567.66236111111</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>45698.54001157408</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>45819.37796296296</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45261.61618055555</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45740</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45574.38811342593</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45819.44628472222</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>44728.36199074074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>45819.48962962963</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45819.55990740741</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45819.4068287037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45820.40336805556</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45819.39910879629</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45153.48958333334</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45408.60974537037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45819.41706018519</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45819.61023148148</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45187.45697916667</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45824.5883912037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45821.57449074074</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45824.53961805555</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45387.55202546297</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45825.64038194445</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45825.64649305555</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -31197,7 +31197,7 @@
         <v>45825.61914351852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -31259,7 +31259,7 @@
         <v>44791</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -31316,7 +31316,7 @@
         <v>45013.65927083333</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45754.35976851852</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>45211.42238425926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>45826.43805555555</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>44967</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -31601,7 +31601,7 @@
         <v>45527.34408564815</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45825.64113425926</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45825.37327546296</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>44203</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>44524.56090277778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45827</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45194.58666666667</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44749.65376157407</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45827.47149305556</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45219</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45707.59410879629</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45827.48033564815</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45613.775625</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45278.49693287037</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>44943.64569444444</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45204</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45827.4880787037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45827</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>45701</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45827</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45827</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>44187</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45597.74361111111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -32994,7 +32994,7 @@
         <v>45460.66142361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33051,7 +33051,7 @@
         <v>45568.5949537037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>45831.58878472223</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44704.34877314815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45579.3487962963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45331</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -33341,7 +33341,7 @@
         <v>45238.34386574074</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>44774.92517361111</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45831.50133101852</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>45061</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -33569,7 +33569,7 @@
         <v>45246</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -33626,7 +33626,7 @@
         <v>45831.50354166667</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>45212</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>45873.52091435185</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -33797,7 +33797,7 @@
         <v>45377.3715625</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>45475.5766087963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -33911,7 +33911,7 @@
         <v>45834.60839120371</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45219.56564814815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45448</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45719</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45716.37511574074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -34196,7 +34196,7 @@
         <v>45875.46909722222</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45834.46130787037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>45527.46644675926</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45833.44599537037</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45713.47555555555</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -34486,7 +34486,7 @@
         <v>45713.56700231481</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>44239</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45834.44530092592</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -34657,7 +34657,7 @@
         <v>45257</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>44897</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>44831.36085648148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45835.57047453704</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>44706</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45622.5512037037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45712.40818287037</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45271.49274305555</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45280.65898148148</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45629.68210648148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45415</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45223.53648148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>44505</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45506.34135416667</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45835.34876157407</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>45719.49319444445</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -35589,7 +35589,7 @@
         <v>45123</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -35646,7 +35646,7 @@
         <v>45838.62444444445</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>45838.60077546296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45838.60314814815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45880.46456018519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>44749.65293981481</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45149</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45835.32489583334</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>45835.54614583333</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45838.33667824074</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45835.34113425926</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45478.46400462963</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -36288,7 +36288,7 @@
         <v>44967.48270833334</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>44806</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45565.64587962963</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45624.46519675926</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45611.43383101852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44952</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45646.57283564815</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45251</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45840.5125</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45840.55234953704</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>45474.7375925926</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>44631</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>44995.54887731482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>44489</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45265.66679398148</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37153,7 +37153,7 @@
         <v>45583.36581018518</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44511</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>45672.40888888889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45672.45166666667</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45014.3017824074</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>44869.489375</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>44840</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45793</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45840</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>45560.57574074074</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45310.43618055555</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45755.35984953704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>45474.47489583334</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45610.63042824074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45608.56155092592</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45840.67278935185</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45555.43184027778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45453</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>45103.4828587963</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>45712.61496527777</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>44999.57931712963</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45838.31546296296</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45702</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>44839</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -38541,7 +38541,7 @@
         <v>45631</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>45677.58137731482</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -38655,7 +38655,7 @@
         <v>44830</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>44355.59233796296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>45169</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         <v>45743.60083333333</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -38888,7 +38888,7 @@
         <v>45881.69613425926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45881.7040162037</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45205</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39059,7 +39059,7 @@
         <v>45119.56549768519</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45882</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39173,7 +39173,7 @@
         <v>45639.28372685185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>45497.28417824074</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>44872.58997685185</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>45114</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>45607.34104166667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>44883</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45736.39627314815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>45881.70878472222</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45881.6999074074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>45299.4562037037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45729.27089120371</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45644.57359953703</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44796</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45842.64752314815</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45527.30645833333</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45469.49199074074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45478.61697916667</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45478.62592592592</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>44110</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45883.37849537037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -40338,7 +40338,7 @@
         <v>45884.44887731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>44383</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -40462,7 +40462,7 @@
         <v>45883.36921296296</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>45883.375</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>44732</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -40633,7 +40633,7 @@
         <v>44370</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45705.58114583333</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45545</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>45747.38574074074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>44381</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>44382</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -40990,7 +40990,7 @@
         <v>45468.63453703704</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41047,7 +41047,7 @@
         <v>44865.47965277778</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41104,7 +41104,7 @@
         <v>45244</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45486.76454861111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>44904.6508912037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45482.70034722222</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>45743.52796296297</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -41394,7 +41394,7 @@
         <v>45698.53550925926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -41451,7 +41451,7 @@
         <v>45884.55987268518</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45646</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45660</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>44364</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -41684,7 +41684,7 @@
         <v>45772.57445601852</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>44944</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45677.57865740741</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v